--- a/app/public/templates/client-balances-template.xlsx
+++ b/app/public/templates/client-balances-template.xlsx
@@ -448,10 +448,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="80" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -463,43 +463,51 @@
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Заполните лист «Остатки»: по строке на клиента-родителя.</t>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Заполните лист «Остатки»: ОДИН клиент — ОДНА строка (один телефон).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Если один и тот же телефон попадёт в несколько строк — балансы сложатся (клиент получит задвоенную сумму).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>• Телефон — как в CRM (берутся только цифры).</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>• Баланс на сегодня — итоговый остаток: + депозит/переплата, − долг.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Загрузка: «Импорт базы» → «Обновить остатки».</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Баланс каждого клиента ставится РОВНО к значению из файла (по телефону).</t>
-        </is>
-      </c>
-    </row>
+          <t>• Баланс на сегодня — итоговый остаток клиента: + депозит/переплата, − долг.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
+        <is>
+          <t>Загрузка: «Импорт базы» → «Обновить остатки».</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Баланс каждого клиента ставится РОВНО к значению из файла (по телефону).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Клиентов не создаёт, в ДДС не пишет. Повторная загрузка того же файла ничего не меняет.</t>
         </is>
